--- a/data/trending_integrated_20260923_09.xlsx
+++ b/data/trending_integrated_20260923_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31250</v>
+        <v>19100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+0.64%</t>
+          <t>'+15.48%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.21</v>
+        <v>-0.15</v>
       </c>
       <c r="E2" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="G2" t="n">
-        <v>593</v>
+        <v>132</v>
       </c>
       <c r="H2" t="n">
-        <v>16.63</v>
+        <v>0.62</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>31050</v>
+        <v>16540</v>
       </c>
       <c r="K2" t="n">
-        <v>31300</v>
+        <v>17530</v>
       </c>
       <c r="L2" t="n">
-        <v>31500</v>
+        <v>19630</v>
       </c>
       <c r="M2" t="n">
-        <v>31250</v>
+        <v>17500</v>
       </c>
       <c r="N2" t="n">
-        <v>16.42</v>
+        <v>0.77</v>
       </c>
       <c r="O2" t="n">
-        <v>355319400</v>
+        <v>94422437620</v>
       </c>
       <c r="P2" t="n">
-        <v>69200</v>
+        <v>30550</v>
       </c>
       <c r="Q2" t="n">
-        <v>24150</v>
+        <v>6100</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,29 +626,489 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 릴레이테라퓨틱스 상승 및 간암/담관암 결과 발표 기대감. 공시 지연 및 주가 관련 상반된 전망 존재.</t>
+          <t>미국 양자 관련주 급등에 따른 엑스게이트 주가 상승 기대. 국내 양자암호통신망 시뮬레이터 개발 뉴스 및 공매도 세력에 대한 경계.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>['양자', '암호통신', '공매도']</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>356680</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>284000</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>'+2.71%</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E3" t="n">
+        <v>624</v>
+      </c>
+      <c r="F3" t="n">
+        <v>381</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2758</v>
+      </c>
+      <c r="H3" t="n">
+        <v>46.55</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>276500</v>
+      </c>
+      <c r="K3" t="n">
+        <v>284500</v>
+      </c>
+      <c r="L3" t="n">
+        <v>285000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>283000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="O3" t="n">
+        <v>617577270000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>82400</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>미국 증시 반도체 선물 급등 및 메모리 반도체 호황에 따른 주가 상승 기대감. 그러나 정치적 언급과 함께 개인 투자자들의 기대감만 존재하는 상황.</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>['반도체', '선물', '메모리']</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>112</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1879000</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>'+2.12%</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E4" t="n">
+        <v>678</v>
+      </c>
+      <c r="F4" t="n">
+        <v>427</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2769</v>
+      </c>
+      <c r="H4" t="n">
+        <v>50.15</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1840000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1899000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1873000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>50.17</v>
+      </c>
+      <c r="O4" t="n">
+        <v>624083409000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>333000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>미국 증시 신고가 및 반도체 급등에 따른 SK하이닉스 주가 상승 기대. 야간 선물 상승세를 바탕으로 200만원 돌파 가능성에 대한 언급.</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
         <v>0.2</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>['릴레이테라퓨틱스', '담관암', '승인']</t>
-        </is>
-      </c>
-      <c r="X2" t="n">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>['반도체', '야간선물', '상승추세']</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>77</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>31550</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'+1.61%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E5" t="n">
+        <v>103</v>
+      </c>
+      <c r="F5" t="n">
+        <v>81</v>
+      </c>
+      <c r="G5" t="n">
+        <v>633</v>
+      </c>
+      <c r="H5" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>31050</v>
+      </c>
+      <c r="K5" t="n">
+        <v>31300</v>
+      </c>
+      <c r="L5" t="n">
+        <v>31550</v>
+      </c>
+      <c r="M5" t="n">
+        <v>30900</v>
+      </c>
+      <c r="N5" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1053939350</v>
+      </c>
+      <c r="P5" t="n">
+        <v>69200</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>24150</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>미국 릴레이테라퓨틱스의 상승 및 신약 승인 기대감. 간암 및 담관암 임상 결과 발표를 앞두고 주가 변동성 예상 및 공매도 세력과의 눈치 싸움.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>['신약', '임상', '공매도']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
         <v>2</v>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>028300</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>85250</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'-1.45%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E6" t="n">
+        <v>117</v>
+      </c>
+      <c r="F6" t="n">
+        <v>87</v>
+      </c>
+      <c r="G6" t="n">
+        <v>326</v>
+      </c>
+      <c r="H6" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>86500</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86100</v>
+      </c>
+      <c r="L6" t="n">
+        <v>86100</v>
+      </c>
+      <c r="M6" t="n">
+        <v>84900</v>
+      </c>
+      <c r="N6" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>28056165950</v>
+      </c>
+      <c r="P6" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>미국 증시 호조에도 불구하고 주가 상승 모멘텀 부재. 소형 SMR 및 원전 관련 기대감에도 불구하고 주가 하락 및 조정 가능성 언급.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['SMR', '원전', '조정']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>18040</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'-4.04%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E7" t="n">
+        <v>41</v>
+      </c>
+      <c r="F7" t="n">
+        <v>31</v>
+      </c>
+      <c r="G7" t="n">
+        <v>127</v>
+      </c>
+      <c r="H7" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>18800</v>
+      </c>
+      <c r="K7" t="n">
+        <v>18800</v>
+      </c>
+      <c r="L7" t="n">
+        <v>18800</v>
+      </c>
+      <c r="M7" t="n">
+        <v>17870</v>
+      </c>
+      <c r="N7" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="O7" t="n">
+        <v>24122281110</v>
+      </c>
+      <c r="P7" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>공매도 및 기관 매도세에 대한 불만과 함께 대차 해지 운동 촉구. 원전 관련 기대감에도 불구하고 주가 하락으로 인한 실망감이 큼.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['공매도', '대차해지', '원전']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>047040</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260923_09.xlsx
+++ b/data/trending_integrated_20260923_09.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19100</v>
+        <v>19850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+15.48%</t>
+          <t>'+20.01%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.15</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G2" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -601,7 +601,7 @@
         <v>17530</v>
       </c>
       <c r="L2" t="n">
-        <v>19630</v>
+        <v>19880</v>
       </c>
       <c r="M2" t="n">
         <v>17500</v>
@@ -610,7 +610,7 @@
         <v>0.77</v>
       </c>
       <c r="O2" t="n">
-        <v>94422437620</v>
+        <v>135483878410</v>
       </c>
       <c r="P2" t="n">
         <v>30550</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 양자 관련주 급등에 따른 엑스게이트 주가 상승 기대. 국내 양자암호통신망 시뮬레이터 개발 뉴스 및 공매도 세력에 대한 경계.</t>
+          <t>미국 양자 관련주 급등에 따른 긍정적 전망과 함께, 어제 공매도 세력의 누름에도 불구하고 주가 상승에 대한 기대감이 나타남. 아이온큐 관련 내용 구체적 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['양자', '암호통신', '공매도']</t>
+          <t>['양자', '아이온큐', '공매도']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>284000</v>
+        <v>283250</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+2.71%</t>
+          <t>'+2.44%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>624</v>
+        <v>674</v>
       </c>
       <c r="F3" t="n">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="G3" t="n">
-        <v>2758</v>
+        <v>2933</v>
       </c>
       <c r="H3" t="n">
         <v>46.55</v>
@@ -702,7 +702,7 @@
         <v>46.56</v>
       </c>
       <c r="O3" t="n">
-        <v>617577270000</v>
+        <v>762151383250</v>
       </c>
       <c r="P3" t="n">
         <v>374500</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1879000</v>
+        <v>1864000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.12%</t>
+          <t>'+1.30%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>678</v>
+        <v>767</v>
       </c>
       <c r="F4" t="n">
-        <v>427</v>
+        <v>468</v>
       </c>
       <c r="G4" t="n">
-        <v>2769</v>
+        <v>2882</v>
       </c>
       <c r="H4" t="n">
         <v>50.15</v>
@@ -788,13 +788,13 @@
         <v>1900000</v>
       </c>
       <c r="M4" t="n">
-        <v>1873000</v>
+        <v>1863000</v>
       </c>
       <c r="N4" t="n">
         <v>50.17</v>
       </c>
       <c r="O4" t="n">
-        <v>624083409000</v>
+        <v>911345191500</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31550</v>
+        <v>31200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.61%</t>
+          <t>'+0.48%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.21</v>
       </c>
       <c r="E5" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F5" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G5" t="n">
-        <v>633</v>
+        <v>681</v>
       </c>
       <c r="H5" t="n">
         <v>16.63</v>
@@ -886,7 +886,7 @@
         <v>16.42</v>
       </c>
       <c r="O5" t="n">
-        <v>1053939350</v>
+        <v>1519713650</v>
       </c>
       <c r="P5" t="n">
         <v>69200</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 릴레이테라퓨틱스의 상승 및 신약 승인 기대감. 간암 및 담관암 임상 결과 발표를 앞두고 주가 변동성 예상 및 공매도 세력과의 눈치 싸움.</t>
+          <t>미국 릴레이테라퓨틱스의 상승 및 HLB 관련 신약 승인 기대감이 제기되었으나, 주가 흐름에 대한 불만과 공매도 관련 언급도 존재함. 간암, 담관암 관련 내용 포함.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['신약', '임상', '공매도']</t>
+          <t>['신약', '승인', '공매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>85250</v>
+        <v>85100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.45%</t>
+          <t>'-1.62%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="F6" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>326</v>
+        <v>372</v>
       </c>
       <c r="H6" t="n">
         <v>23.03</v>
@@ -972,13 +972,13 @@
         <v>86100</v>
       </c>
       <c r="M6" t="n">
-        <v>84900</v>
+        <v>84700</v>
       </c>
       <c r="N6" t="n">
         <v>23.05</v>
       </c>
       <c r="O6" t="n">
-        <v>28056165950</v>
+        <v>39903392100</v>
       </c>
       <c r="P6" t="n">
         <v>139200</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 증시 호조에도 불구하고 주가 상승 모멘텀 부재. 소형 SMR 및 원전 관련 기대감에도 불구하고 주가 하락 및 조정 가능성 언급.</t>
+          <t>미국 시장 호조와 원전 관련 긍정적 전망에도 불구하고 주가 부진에 대한 언급이 있으며, 공매도에 대한 불만이 제기됨. 소형SMR, 한국형 원전 관련 내용 포함.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['SMR', '원전', '조정']</t>
+          <t>['원전', '공매도', 'SMR']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18040</v>
+        <v>18020</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-4.04%</t>
+          <t>'-4.15%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="H7" t="n">
         <v>10.38</v>
@@ -1064,13 +1064,13 @@
         <v>18800</v>
       </c>
       <c r="M7" t="n">
-        <v>17870</v>
+        <v>17830</v>
       </c>
       <c r="N7" t="n">
         <v>10.47</v>
       </c>
       <c r="O7" t="n">
-        <v>24122281110</v>
+        <v>36706884240</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>공매도 및 기관 매도세에 대한 불만과 함께 대차 해지 운동 촉구. 원전 관련 기대감에도 불구하고 주가 하락으로 인한 실망감이 큼.</t>
+          <t>원전 관련 이슈 속에서 공매도 관련 언급과 함께 주가 하락에 대한 불만이 제기됨. 사실 기반 정보보다는 감정적 표현이 주를 이룸.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지', '원전']</t>
+          <t>['원전', '공매도', '주가']</t>
         </is>
       </c>
       <c r="X7" t="n">

--- a/data/trending_integrated_20260923_09.xlsx
+++ b/data/trending_integrated_20260923_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19850</v>
+        <v>19420</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+20.01%</t>
+          <t>'+17.41%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.15</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="F2" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="G2" t="n">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -601,7 +601,7 @@
         <v>17530</v>
       </c>
       <c r="L2" t="n">
-        <v>19880</v>
+        <v>19950</v>
       </c>
       <c r="M2" t="n">
         <v>17500</v>
@@ -610,7 +610,7 @@
         <v>0.77</v>
       </c>
       <c r="O2" t="n">
-        <v>135483878410</v>
+        <v>175862405050</v>
       </c>
       <c r="P2" t="n">
         <v>30550</v>
@@ -619,23 +619,23 @@
         <v>6100</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>94000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 양자 관련주 급등에 따른 긍정적 전망과 함께, 어제 공매도 세력의 누름에도 불구하고 주가 상승에 대한 기대감이 나타남. 아이온큐 관련 내용 구체적 언급.</t>
+          <t>미국 양자 관련주 급등에 따른 엑스게이트 주가 상승 기대. 아이온큐 급등 및 양자 보안 상용화 관련 호재.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['양자', '아이온큐', '공매도']</t>
+          <t>['양자', '아이온큐', '보안']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>283250</v>
+        <v>284500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+2.44%</t>
+          <t>'+2.89%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>674</v>
+        <v>708</v>
       </c>
       <c r="F3" t="n">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="G3" t="n">
-        <v>2933</v>
+        <v>3060</v>
       </c>
       <c r="H3" t="n">
         <v>46.55</v>
@@ -702,7 +702,7 @@
         <v>46.56</v>
       </c>
       <c r="O3" t="n">
-        <v>762151383250</v>
+        <v>914091156250</v>
       </c>
       <c r="P3" t="n">
         <v>374500</v>
@@ -711,14 +711,14 @@
         <v>82400</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>729000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 증시 반도체 선물 급등 및 메모리 반도체 호황에 따른 주가 상승 기대감. 그러나 정치적 언급과 함께 개인 투자자들의 기대감만 존재하는 상황.</t>
+          <t>미국 증시 반도체 선물 급등에 따른 삼성전자 주가 30만원 돌파 기대감. 22년 추석 후 통계 기반 상승 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체', '선물', '메모리']</t>
+          <t>['반도체', '선물', '통계']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1864000</v>
+        <v>1877000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.30%</t>
+          <t>'+2.01%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>767</v>
+        <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="G4" t="n">
-        <v>2882</v>
+        <v>2657</v>
       </c>
       <c r="H4" t="n">
         <v>50.15</v>
@@ -794,7 +794,7 @@
         <v>50.17</v>
       </c>
       <c r="O4" t="n">
-        <v>911345191500</v>
+        <v>1095574009000</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -803,23 +803,23 @@
         <v>333000</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 증시 신고가 및 반도체 급등에 따른 SK하이닉스 주가 상승 기대. 야간 선물 상승세를 바탕으로 200만원 돌파 가능성에 대한 언급.</t>
+          <t>미국 증시 신고가 및 반도체 급등에 따른 SK하이닉스 20만원 돌파 및 상승 추세 정착 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '야간선물', '상승추세']</t>
+          <t>['반도체', '상승 추세', '급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31200</v>
+        <v>17930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.48%</t>
+          <t>'+0.67%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.21</v>
+        <v>-0.76</v>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="F5" t="n">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>681</v>
+        <v>286</v>
       </c>
       <c r="H5" t="n">
-        <v>16.63</v>
+        <v>5.46</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>31050</v>
+        <v>17810</v>
       </c>
       <c r="K5" t="n">
-        <v>31300</v>
+        <v>17950</v>
       </c>
       <c r="L5" t="n">
-        <v>31550</v>
+        <v>17960</v>
       </c>
       <c r="M5" t="n">
-        <v>30900</v>
+        <v>17410</v>
       </c>
       <c r="N5" t="n">
-        <v>16.42</v>
+        <v>6.22</v>
       </c>
       <c r="O5" t="n">
-        <v>1519713650</v>
+        <v>37042327355</v>
       </c>
       <c r="P5" t="n">
-        <v>69200</v>
+        <v>31500</v>
       </c>
       <c r="Q5" t="n">
-        <v>24150</v>
+        <v>1272</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-116000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 릴레이테라퓨틱스의 상승 및 HLB 관련 신약 승인 기대감이 제기되었으나, 주가 흐름에 대한 불만과 공매도 관련 언급도 존재함. 간암, 담관암 관련 내용 포함.</t>
+          <t>미국 증시 급등 및 코스닥 출발 호조에 따른 대한광통신 2만원 돌파 기대. 공매도 세력과의 대립 및 쇼티지 현상 가능성.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['신약', '승인', '공매도']</t>
+          <t>['쇼티지', '공매도', '수급']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>85100</v>
+        <v>30950</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.62%</t>
+          <t>'-0.32%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.02</v>
+        <v>0.21</v>
       </c>
       <c r="E6" t="n">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="F6" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G6" t="n">
-        <v>372</v>
+        <v>714</v>
       </c>
       <c r="H6" t="n">
-        <v>23.03</v>
+        <v>16.63</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>86500</v>
+        <v>31050</v>
       </c>
       <c r="K6" t="n">
-        <v>86100</v>
+        <v>31300</v>
       </c>
       <c r="L6" t="n">
-        <v>86100</v>
+        <v>31550</v>
       </c>
       <c r="M6" t="n">
-        <v>84700</v>
+        <v>30900</v>
       </c>
       <c r="N6" t="n">
-        <v>23.05</v>
+        <v>16.42</v>
       </c>
       <c r="O6" t="n">
-        <v>39903392100</v>
+        <v>2080964100</v>
       </c>
       <c r="P6" t="n">
-        <v>139200</v>
+        <v>69200</v>
       </c>
       <c r="Q6" t="n">
-        <v>57000</v>
+        <v>24150</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 시장 호조와 원전 관련 긍정적 전망에도 불구하고 주가 부진에 대한 언급이 있으며, 공매도에 대한 불만이 제기됨. 소형SMR, 한국형 원전 관련 내용 포함.</t>
+          <t>미국 릴레이테라퓨틱스 주가 상승 및 간암 리보 DP 결과 발표 기대감. 담관암 승인 가능성 및 단기 50만원 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', '공매도', 'SMR']</t>
+          <t>['리보', '간암', '담관암']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18020</v>
+        <v>84900</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-4.15%</t>
+          <t>'-1.85%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="G7" t="n">
-        <v>147</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>10.38</v>
+        <v>23.03</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,58 +1055,150 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18800</v>
+        <v>86500</v>
       </c>
       <c r="K7" t="n">
-        <v>18800</v>
+        <v>86100</v>
       </c>
       <c r="L7" t="n">
-        <v>18800</v>
+        <v>86100</v>
       </c>
       <c r="M7" t="n">
-        <v>17830</v>
+        <v>84700</v>
       </c>
       <c r="N7" t="n">
-        <v>10.47</v>
+        <v>23.05</v>
       </c>
       <c r="O7" t="n">
-        <v>36706884240</v>
+        <v>46612468100</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>57000</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-98000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>원전 관련 이슈 속에서 공매도 관련 언급과 함께 주가 하락에 대한 불만이 제기됨. 사실 기반 정보보다는 감정적 표현이 주를 이룸.</t>
+          <t>미국 증시 및 분위기 양호에도 불구하고 주가 하락. 소형SMR, 한국형 원전 수주 기대와 트럼프 SNS 언급에 대한 불확실성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '주가']</t>
+          <t>['SMR', '원전', '트럼프']</t>
         </is>
       </c>
       <c r="X7" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>17940</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'-4.57%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E8" t="n">
+        <v>59</v>
+      </c>
+      <c r="F8" t="n">
+        <v>42</v>
+      </c>
+      <c r="G8" t="n">
+        <v>162</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>18800</v>
+      </c>
+      <c r="K8" t="n">
+        <v>18800</v>
+      </c>
+      <c r="L8" t="n">
+        <v>18800</v>
+      </c>
+      <c r="M8" t="n">
+        <v>17830</v>
+      </c>
+      <c r="N8" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="O8" t="n">
+        <v>43526868630</v>
+      </c>
+      <c r="P8" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-541000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>미 건설 원전 선물 급등에도 불구하고 주가 하락. 공매도 세력과의 전쟁 및 대차해지 운동 강조.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['공매도', '대차해지', '원전']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
         <v>22</v>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>047040</t>
         </is>

--- a/data/trending_integrated_20260923_09.xlsx
+++ b/data/trending_integrated_20260923_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19420</v>
+        <v>19320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.41%</t>
+          <t>'+16.81%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.15</v>
       </c>
       <c r="E2" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F2" t="n">
         <v>67</v>
       </c>
       <c r="G2" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -610,7 +610,7 @@
         <v>0.77</v>
       </c>
       <c r="O2" t="n">
-        <v>175862405050</v>
+        <v>194349676880</v>
       </c>
       <c r="P2" t="n">
         <v>30550</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 양자 관련주 급등에 따른 엑스게이트 주가 상승 기대. 아이온큐 급등 및 양자 보안 상용화 관련 호재.</t>
+          <t>미국 양자 관련주 급등에 따른 엑스게이트 상승 기대. 공매도 세력과의 대립.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['양자', '아이온큐', '보안']</t>
+          <t>['양자', '보안', '공매도']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>284500</v>
+        <v>285000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+2.89%</t>
+          <t>'+3.07%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>708</v>
+        <v>760</v>
       </c>
       <c r="F3" t="n">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="G3" t="n">
-        <v>3060</v>
+        <v>3202</v>
       </c>
       <c r="H3" t="n">
         <v>46.55</v>
@@ -702,7 +702,7 @@
         <v>46.56</v>
       </c>
       <c r="O3" t="n">
-        <v>914091156250</v>
+        <v>1142761396500</v>
       </c>
       <c r="P3" t="n">
         <v>374500</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 증시 반도체 선물 급등에 따른 삼성전자 주가 30만원 돌파 기대감. 22년 추석 후 통계 기반 상승 전망.</t>
+          <t>미국 선물 급등에 따른 30만원 터치 기대감. 추석 후 상승 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체', '선물', '통계']</t>
+          <t>['선물', '반도체', '추세']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1877000</v>
+        <v>8730</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.01%</t>
+          <t>'+3.07%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>41</v>
       </c>
       <c r="F4" t="n">
-        <v>482</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>2657</v>
+        <v>113</v>
       </c>
       <c r="H4" t="n">
-        <v>50.15</v>
+        <v>26.63</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1840000</v>
+        <v>8470</v>
       </c>
       <c r="K4" t="n">
-        <v>1899000</v>
+        <v>8510</v>
       </c>
       <c r="L4" t="n">
-        <v>1900000</v>
+        <v>8870</v>
       </c>
       <c r="M4" t="n">
-        <v>1863000</v>
+        <v>8480</v>
       </c>
       <c r="N4" t="n">
-        <v>50.17</v>
+        <v>26.58</v>
       </c>
       <c r="O4" t="n">
-        <v>1095574009000</v>
+        <v>10086730820</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>17950</v>
       </c>
       <c r="Q4" t="n">
-        <v>333000</v>
+        <v>8120</v>
       </c>
       <c r="R4" t="n">
-        <v>38000</v>
+        <v>145000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 증시 신고가 및 반도체 급등에 따른 SK하이닉스 20만원 돌파 및 상승 추세 정착 기대.</t>
+          <t>장기 적자 및 부채 부담 속 LG 로봇 관련 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '상승 추세', '급등']</t>
+          <t>['적자', '부채', '로봇']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17930</v>
+        <v>1870000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.67%</t>
+          <t>'+1.63%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.76</v>
+        <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>478</v>
       </c>
       <c r="G5" t="n">
-        <v>286</v>
+        <v>2375</v>
       </c>
       <c r="H5" t="n">
-        <v>5.46</v>
+        <v>50.15</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>17810</v>
+        <v>1840000</v>
       </c>
       <c r="K5" t="n">
-        <v>17950</v>
+        <v>1899000</v>
       </c>
       <c r="L5" t="n">
-        <v>17960</v>
+        <v>1900000</v>
       </c>
       <c r="M5" t="n">
-        <v>17410</v>
+        <v>1862000</v>
       </c>
       <c r="N5" t="n">
-        <v>6.22</v>
+        <v>50.17</v>
       </c>
       <c r="O5" t="n">
-        <v>37042327355</v>
+        <v>1260049223500</v>
       </c>
       <c r="P5" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1272</v>
+        <v>333000</v>
       </c>
       <c r="R5" t="n">
-        <v>-116000</v>
+        <v>38000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 증시 급등 및 코스닥 출발 호조에 따른 대한광통신 2만원 돌파 기대. 공매도 세력과의 대립 및 쇼티지 현상 가능성.</t>
+          <t>미국 반도체 급등에 따른 연휴 후 200만원 이상 상승 추세 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['쇼티지', '공매도', '수급']</t>
+          <t>['반도체', '추세', '야간선물']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30950</v>
+        <v>17860</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.32%</t>
+          <t>'+0.28%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.21</v>
+        <v>-0.76</v>
       </c>
       <c r="E6" t="n">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="F6" t="n">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>714</v>
+        <v>311</v>
       </c>
       <c r="H6" t="n">
-        <v>16.63</v>
+        <v>5.46</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>31050</v>
+        <v>17810</v>
       </c>
       <c r="K6" t="n">
-        <v>31300</v>
+        <v>17950</v>
       </c>
       <c r="L6" t="n">
-        <v>31550</v>
+        <v>18050</v>
       </c>
       <c r="M6" t="n">
-        <v>30900</v>
+        <v>17410</v>
       </c>
       <c r="N6" t="n">
-        <v>16.42</v>
+        <v>6.22</v>
       </c>
       <c r="O6" t="n">
-        <v>2080964100</v>
+        <v>55839822420</v>
       </c>
       <c r="P6" t="n">
-        <v>69200</v>
+        <v>31500</v>
       </c>
       <c r="Q6" t="n">
-        <v>24150</v>
+        <v>1272</v>
       </c>
       <c r="R6" t="n">
-        <v>-7000</v>
+        <v>-116000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 릴레이테라퓨틱스 주가 상승 및 간암 리보 DP 결과 발표 기대감. 담관암 승인 가능성 및 단기 50만원 전망.</t>
+          <t>2만원 돌파 기대감 속 외인 및 기관 매도세 관찰. 광통신 섹터.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['리보', '간암', '담관암']</t>
+          <t>['광통신', '수급', '외인']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>84900</v>
+        <v>30900</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.85%</t>
+          <t>'-0.48%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.02</v>
+        <v>0.21</v>
       </c>
       <c r="E7" t="n">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="F7" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>766</v>
       </c>
       <c r="H7" t="n">
-        <v>23.03</v>
+        <v>16.63</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>86500</v>
+        <v>31050</v>
       </c>
       <c r="K7" t="n">
-        <v>86100</v>
+        <v>31300</v>
       </c>
       <c r="L7" t="n">
-        <v>86100</v>
+        <v>31550</v>
       </c>
       <c r="M7" t="n">
-        <v>84700</v>
+        <v>30600</v>
       </c>
       <c r="N7" t="n">
-        <v>23.05</v>
+        <v>16.42</v>
       </c>
       <c r="O7" t="n">
-        <v>46612468100</v>
+        <v>2975708700</v>
       </c>
       <c r="P7" t="n">
-        <v>139200</v>
+        <v>69200</v>
       </c>
       <c r="Q7" t="n">
-        <v>57000</v>
+        <v>24150</v>
       </c>
       <c r="R7" t="n">
-        <v>-98000</v>
+        <v>-7000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 증시 및 분위기 양호에도 불구하고 주가 하락. 소형SMR, 한국형 원전 수주 기대와 트럼프 SNS 언급에 대한 불확실성.</t>
+          <t>미국 릴레이테라퓨틱스 주가 상승 및 간암 리보 DP 결과 발표 기대감. 담관암 승인 가능성 및 단기 50만원 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['SMR', '원전', '트럼프']</t>
+          <t>['리보', '간암', '담관암']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17940</v>
+        <v>84350</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-4.57%</t>
+          <t>'-2.49%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>59</v>
+        <v>170</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="G8" t="n">
-        <v>162</v>
+        <v>494</v>
       </c>
       <c r="H8" t="n">
-        <v>10.38</v>
+        <v>23.03</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,58 +1147,242 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18800</v>
+        <v>86500</v>
       </c>
       <c r="K8" t="n">
-        <v>18800</v>
+        <v>86100</v>
       </c>
       <c r="L8" t="n">
-        <v>18800</v>
+        <v>86100</v>
       </c>
       <c r="M8" t="n">
-        <v>17830</v>
+        <v>84200</v>
       </c>
       <c r="N8" t="n">
-        <v>10.47</v>
+        <v>23.05</v>
       </c>
       <c r="O8" t="n">
-        <v>43526868630</v>
+        <v>62089003450</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>-541000</v>
+        <v>-98000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미 건설 원전 선물 급등에도 불구하고 주가 하락. 공매도 세력과의 전쟁 및 대차해지 운동 강조.</t>
+          <t>미국 증시 및 소형 SMR 관련 긍정적 분위기. 트럼프 일정 및 수급 불확실성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['SMR', '원전', '수급']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>49450</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'-3.42%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>43</v>
+      </c>
+      <c r="F9" t="n">
+        <v>28</v>
+      </c>
+      <c r="G9" t="n">
+        <v>59</v>
+      </c>
+      <c r="H9" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>51200</v>
+      </c>
+      <c r="K9" t="n">
+        <v>51600</v>
+      </c>
+      <c r="L9" t="n">
+        <v>51600</v>
+      </c>
+      <c r="M9" t="n">
+        <v>49300</v>
+      </c>
+      <c r="N9" t="n">
+        <v>38.44</v>
+      </c>
+      <c r="O9" t="n">
+        <v>32948302550</v>
+      </c>
+      <c r="P9" t="n">
+        <v>67300</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>23150</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-102000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>5조 수주에도 불구하고 주가 하락 지속. 공매도 및 IR 발표 불신.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
         <v>0.2</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>['공매도', '대차해지', '원전']</t>
-        </is>
-      </c>
-      <c r="X8" t="n">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['수주', '공매도', 'IR']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>17880</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'-4.89%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>65</v>
+      </c>
+      <c r="F10" t="n">
+        <v>44</v>
+      </c>
+      <c r="G10" t="n">
+        <v>181</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>18800</v>
+      </c>
+      <c r="K10" t="n">
+        <v>18800</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18800</v>
+      </c>
+      <c r="M10" t="n">
+        <v>17830</v>
+      </c>
+      <c r="N10" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="O10" t="n">
+        <v>49875342565</v>
+      </c>
+      <c r="P10" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-541000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>대차 해지 운동 및 공매도 파산 기대감. 그러나 주가 하락 및 원전 수주 불확실성.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['공매도', '대차', '원전']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
         <v>22</v>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>047040</t>
         </is>

--- a/data/trending_integrated_20260923_09.xlsx
+++ b/data/trending_integrated_20260923_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>토마토시스템</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19320</v>
+        <v>4305</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+16.81%</t>
+          <t>'+29.86%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.15</v>
+        <v>-1.02</v>
       </c>
       <c r="E2" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>162</v>
+        <v>33</v>
       </c>
       <c r="H2" t="n">
-        <v>0.62</v>
+        <v>1.63</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>16540</v>
+        <v>3315</v>
       </c>
       <c r="K2" t="n">
-        <v>17530</v>
+        <v>3310</v>
       </c>
       <c r="L2" t="n">
-        <v>19950</v>
+        <v>4305</v>
       </c>
       <c r="M2" t="n">
-        <v>17500</v>
+        <v>3070</v>
       </c>
       <c r="N2" t="n">
-        <v>0.77</v>
+        <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>194349676880</v>
+        <v>30572868743</v>
       </c>
       <c r="P2" t="n">
-        <v>30550</v>
+        <v>6950</v>
       </c>
       <c r="Q2" t="n">
-        <v>6100</v>
+        <v>1809</v>
       </c>
       <c r="R2" t="n">
-        <v>94000</v>
+        <v>-1000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 양자 관련주 급등에 따른 엑스게이트 상승 기대. 공매도 세력과의 대립.</t>
+          <t>3연상 기록 후 AI 관련주 동반 상승 기대감. 단기 급등 이후 폭락 가능성 및 투자 주의 요구.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['양자', '보안', '공매도']</t>
+          <t>['3연상', 'AI', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>393210</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>285000</v>
+        <v>18960</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+3.07%</t>
+          <t>'+14.63%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.01</v>
+        <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>95</v>
       </c>
       <c r="F3" t="n">
-        <v>443</v>
+        <v>75</v>
       </c>
       <c r="G3" t="n">
-        <v>3202</v>
+        <v>170</v>
       </c>
       <c r="H3" t="n">
-        <v>46.55</v>
+        <v>0.62</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>276500</v>
+        <v>16540</v>
       </c>
       <c r="K3" t="n">
-        <v>284500</v>
+        <v>17530</v>
       </c>
       <c r="L3" t="n">
-        <v>285000</v>
+        <v>19950</v>
       </c>
       <c r="M3" t="n">
-        <v>283000</v>
+        <v>17500</v>
       </c>
       <c r="N3" t="n">
-        <v>46.56</v>
+        <v>0.77</v>
       </c>
       <c r="O3" t="n">
-        <v>1142761396500</v>
+        <v>208294479345</v>
       </c>
       <c r="P3" t="n">
-        <v>374500</v>
+        <v>30550</v>
       </c>
       <c r="Q3" t="n">
-        <v>82400</v>
+        <v>6100</v>
       </c>
       <c r="R3" t="n">
-        <v>729000</v>
+        <v>118000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 선물 급등에 따른 30만원 터치 기대감. 추석 후 상승 전망.</t>
+          <t>미국 양자 관련주 급등에 따른 엑스게이트 동반 상승 기대. 공매도 세력의 압박 속 단기 급등 가능성.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['선물', '반도체', '추세']</t>
+          <t>['양자보안', '상승 기대', '공매도']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8730</v>
+        <v>14070</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+3.07%</t>
+          <t>'+3.46%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.05</v>
+        <v>-0.16</v>
       </c>
       <c r="E4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="H4" t="n">
-        <v>26.63</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8470</v>
+        <v>13600</v>
       </c>
       <c r="K4" t="n">
-        <v>8510</v>
+        <v>13750</v>
       </c>
       <c r="L4" t="n">
-        <v>8870</v>
+        <v>15050</v>
       </c>
       <c r="M4" t="n">
-        <v>8480</v>
+        <v>13750</v>
       </c>
       <c r="N4" t="n">
-        <v>26.58</v>
+        <v>9.77</v>
       </c>
       <c r="O4" t="n">
-        <v>10086730820</v>
+        <v>72372801890</v>
       </c>
       <c r="P4" t="n">
-        <v>17950</v>
+        <v>23550</v>
       </c>
       <c r="Q4" t="n">
-        <v>8120</v>
+        <v>5780</v>
       </c>
       <c r="R4" t="n">
-        <v>145000</v>
+        <v>275000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-64000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>장기 적자 및 부채 부담 속 LG 로봇 관련 기대감.</t>
+          <t>개인 투자자들의 단기 매매 및 감사원 주가 조작 의혹 제기. 외인·기관의 매도세 관찰.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['적자', '부채', '로봇']</t>
+          <t>['주가 조작', '외인 매매', '단기 매매']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1870000</v>
+        <v>8700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.63%</t>
+          <t>'+2.72%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>44</v>
       </c>
       <c r="F5" t="n">
-        <v>478</v>
+        <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>2375</v>
+        <v>123</v>
       </c>
       <c r="H5" t="n">
-        <v>50.15</v>
+        <v>26.63</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1840000</v>
+        <v>8470</v>
       </c>
       <c r="K5" t="n">
-        <v>1899000</v>
+        <v>8510</v>
       </c>
       <c r="L5" t="n">
-        <v>1900000</v>
+        <v>8870</v>
       </c>
       <c r="M5" t="n">
-        <v>1862000</v>
+        <v>8480</v>
       </c>
       <c r="N5" t="n">
-        <v>50.17</v>
+        <v>26.58</v>
       </c>
       <c r="O5" t="n">
-        <v>1260049223500</v>
+        <v>10880379185</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>17950</v>
       </c>
       <c r="Q5" t="n">
-        <v>333000</v>
+        <v>8120</v>
       </c>
       <c r="R5" t="n">
-        <v>38000</v>
+        <v>359000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 반도체 급등에 따른 연휴 후 200만원 이상 상승 추세 전망.</t>
+          <t>대규모 부채 상환 부담 속 LG그룹주 재평가 기대. 외인·기관의 지속적인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '추세', '야간선물']</t>
+          <t>['부채', 'LG그룹주', '매도세']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17860</v>
+        <v>283750</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.28%</t>
+          <t>'+2.62%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.76</v>
+        <v>-0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>466</v>
       </c>
       <c r="G6" t="n">
-        <v>311</v>
+        <v>3216</v>
       </c>
       <c r="H6" t="n">
-        <v>5.46</v>
+        <v>46.55</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>17810</v>
+        <v>276500</v>
       </c>
       <c r="K6" t="n">
-        <v>17950</v>
+        <v>284500</v>
       </c>
       <c r="L6" t="n">
-        <v>18050</v>
+        <v>285000</v>
       </c>
       <c r="M6" t="n">
-        <v>17410</v>
+        <v>283000</v>
       </c>
       <c r="N6" t="n">
-        <v>6.22</v>
+        <v>46.56</v>
       </c>
       <c r="O6" t="n">
-        <v>55839822420</v>
+        <v>1336514267750</v>
       </c>
       <c r="P6" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>1272</v>
+        <v>82400</v>
       </c>
       <c r="R6" t="n">
-        <v>-116000</v>
+        <v>1308000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>346000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2만원 돌파 기대감 속 외인 및 기관 매도세 관찰. 광통신 섹터.</t>
+          <t>미국 선물 급등에 따른 30만원 터치 기대감. 추석 후 상승 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', '수급', '외인']</t>
+          <t>['선물', '반도체', '추세']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,77 +1016,77 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30900</v>
+        <v>1862000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.48%</t>
+          <t>'+1.20%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.21</v>
+        <v>-0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>128</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>96</v>
+        <v>482</v>
       </c>
       <c r="G7" t="n">
-        <v>766</v>
+        <v>2181</v>
       </c>
       <c r="H7" t="n">
-        <v>16.63</v>
+        <v>50.15</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>31050</v>
+        <v>1840000</v>
       </c>
       <c r="K7" t="n">
-        <v>31300</v>
+        <v>1899000</v>
       </c>
       <c r="L7" t="n">
-        <v>31550</v>
+        <v>1900000</v>
       </c>
       <c r="M7" t="n">
-        <v>30600</v>
+        <v>1859000</v>
       </c>
       <c r="N7" t="n">
-        <v>16.42</v>
+        <v>50.17</v>
       </c>
       <c r="O7" t="n">
-        <v>2975708700</v>
+        <v>1404323727000</v>
       </c>
       <c r="P7" t="n">
-        <v>69200</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>24150</v>
+        <v>333000</v>
       </c>
       <c r="R7" t="n">
-        <v>-7000</v>
+        <v>-28000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 릴레이테라퓨틱스 주가 상승 및 간암 리보 DP 결과 발표 기대감. 담관암 승인 가능성 및 단기 50만원 전망.</t>
+          <t>미국 반도체 시장 강세 및 신고가 경신. 연휴 후 220만~230만 목표 주가 전망. 매수 적정 타임.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['리보', '간암', '담관암']</t>
+          <t>['반도체', '신고가', '매수 타임']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>84350</v>
+        <v>17990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.49%</t>
+          <t>'+1.01%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.02</v>
+        <v>-0.76</v>
       </c>
       <c r="E8" t="n">
-        <v>170</v>
+        <v>57</v>
       </c>
       <c r="F8" t="n">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>494</v>
+        <v>350</v>
       </c>
       <c r="H8" t="n">
-        <v>23.03</v>
+        <v>5.46</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>86500</v>
+        <v>17810</v>
       </c>
       <c r="K8" t="n">
-        <v>86100</v>
+        <v>17950</v>
       </c>
       <c r="L8" t="n">
-        <v>86100</v>
+        <v>18180</v>
       </c>
       <c r="M8" t="n">
-        <v>84200</v>
+        <v>17410</v>
       </c>
       <c r="N8" t="n">
-        <v>23.05</v>
+        <v>6.22</v>
       </c>
       <c r="O8" t="n">
-        <v>62089003450</v>
+        <v>75802569755</v>
       </c>
       <c r="P8" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q8" t="n">
-        <v>57000</v>
+        <v>1272</v>
       </c>
       <c r="R8" t="n">
-        <v>-98000</v>
+        <v>-78000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 증시 및 소형 SMR 관련 긍정적 분위기. 트럼프 일정 및 수급 불확실성.</t>
+          <t>2만원 목표 주가 달성 기대감 속 코스닥 급등 출발. 30% 상승 중 외인 매도세 관찰 및 대규모 매집 준비.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['SMR', '원전', '수급']</t>
+          <t>['2만원 목표', '급등', '외인 매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49450</v>
+        <v>30550</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.42%</t>
+          <t>'-1.61%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.1</v>
+        <v>0.21</v>
       </c>
       <c r="E9" t="n">
-        <v>43</v>
+        <v>140</v>
       </c>
       <c r="F9" t="n">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="G9" t="n">
-        <v>59</v>
+        <v>860</v>
       </c>
       <c r="H9" t="n">
-        <v>38.34</v>
+        <v>16.63</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>51200</v>
+        <v>31050</v>
       </c>
       <c r="K9" t="n">
-        <v>51600</v>
+        <v>31300</v>
       </c>
       <c r="L9" t="n">
-        <v>51600</v>
+        <v>31550</v>
       </c>
       <c r="M9" t="n">
-        <v>49300</v>
+        <v>30500</v>
       </c>
       <c r="N9" t="n">
-        <v>38.44</v>
+        <v>16.42</v>
       </c>
       <c r="O9" t="n">
-        <v>32948302550</v>
+        <v>3919607750</v>
       </c>
       <c r="P9" t="n">
-        <v>67300</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>23150</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>-102000</v>
+        <v>-27000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>5조 수주에도 불구하고 주가 하락 지속. 공매도 및 IR 발표 불신.</t>
+          <t>미국 릴레이테라퓨틱스 상승 및 간암·담관암 리보 결과 발표 기대. 대규모 대차거래 체결 및 상환 동시 발생.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['수주', '공매도', 'IR']</t>
+          <t>['간암', '담관암', '리보']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17880</v>
+        <v>83900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-4.89%</t>
+          <t>'-3.01%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>191</v>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="G10" t="n">
-        <v>181</v>
+        <v>570</v>
       </c>
       <c r="H10" t="n">
-        <v>10.38</v>
+        <v>23.03</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18800</v>
+        <v>86500</v>
       </c>
       <c r="K10" t="n">
-        <v>18800</v>
+        <v>86100</v>
       </c>
       <c r="L10" t="n">
-        <v>18800</v>
+        <v>86100</v>
       </c>
       <c r="M10" t="n">
-        <v>17830</v>
+        <v>83800</v>
       </c>
       <c r="N10" t="n">
-        <v>10.47</v>
+        <v>23.05</v>
       </c>
       <c r="O10" t="n">
-        <v>49875342565</v>
+        <v>74137011200</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>-541000</v>
+        <v>-248000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-42000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대차 해지 운동 및 공매도 파산 기대감. 그러나 주가 하락 및 원전 수주 불확실성.</t>
+          <t>미국 SMR 사업 확정 및 트럼프 발언 기대감 속 원전주 동반 하락. 차트 붕괴 및 신용·공매도 우려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,18 +1371,202 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공매도', '대차', '원전']</t>
+          <t>['SMR', '원전', '트럼프']</t>
         </is>
       </c>
       <c r="X10" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>49250</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'-3.81%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" t="n">
+        <v>31</v>
+      </c>
+      <c r="G11" t="n">
+        <v>67</v>
+      </c>
+      <c r="H11" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>51200</v>
+      </c>
+      <c r="K11" t="n">
+        <v>51600</v>
+      </c>
+      <c r="L11" t="n">
+        <v>51600</v>
+      </c>
+      <c r="M11" t="n">
+        <v>49150</v>
+      </c>
+      <c r="N11" t="n">
+        <v>38.44</v>
+      </c>
+      <c r="O11" t="n">
+        <v>37953908425</v>
+      </c>
+      <c r="P11" t="n">
+        <v>67300</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>23150</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-182000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-21000</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>5조 수주 사실에도 불구하고 주가 하락 지속. 20일선 지지 실패 및 외인 공매도에 대한 불만 표출.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['수주', '주가 하락', '공매도']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>17710</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-5.80%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E12" t="n">
+        <v>80</v>
+      </c>
+      <c r="F12" t="n">
+        <v>55</v>
+      </c>
+      <c r="G12" t="n">
+        <v>213</v>
+      </c>
+      <c r="H12" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>18800</v>
+      </c>
+      <c r="K12" t="n">
+        <v>18800</v>
+      </c>
+      <c r="L12" t="n">
+        <v>18800</v>
+      </c>
+      <c r="M12" t="n">
+        <v>17640</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="O12" t="n">
+        <v>66100558875</v>
+      </c>
+      <c r="P12" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-1005000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-51000</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>미국 원전 관련 긍정 뉴스 기대감 속 공매도 세력과의 대립 심화. 매수세 강하나 주가 하락.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['공매도', '원전', '수주']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
         <v>22</v>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>047040</t>
         </is>
